--- a/diseases/d057/2010-2014.xlsx
+++ b/diseases/d057/2010-2014.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -913,9 +910,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1061,9 +1055,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1801,9 +1792,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2541,9 +2529,6 @@
       <c r="O14" t="n">
         <v>7</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.013980102260254</v>
       </c>
@@ -3429,9 +3414,6 @@
       <c r="O20" t="n">
         <v>4</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.007988629863002287</v>
       </c>
@@ -4169,9 +4151,6 @@
       <c r="O25" t="n">
         <v>10</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.01997157465750572</v>
       </c>
@@ -4909,9 +4888,6 @@
       <c r="O30" t="n">
         <v>6</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.01198294479450343</v>
       </c>
@@ -5797,9 +5773,6 @@
       <c r="O36" t="n">
         <v>2</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -6537,9 +6510,6 @@
       <c r="O41" t="n">
         <v>5</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.009985787328752859</v>
       </c>
@@ -7425,9 +7395,6 @@
       <c r="O47" t="n">
         <v>2</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -8165,9 +8132,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -8905,9 +8869,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9793,9 +9754,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10533,9 +10491,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -11273,9 +11228,6 @@
       <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -12013,9 +11965,6 @@
       <c r="O78" t="n">
         <v>2</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.003957335530340491</v>
       </c>
@@ -12901,9 +12850,6 @@
       <c r="O84" t="n">
         <v>7</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.01385067435619172</v>
       </c>
@@ -13641,9 +13587,6 @@
       <c r="O89" t="n">
         <v>11</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.0217653454168727</v>
       </c>
@@ -14529,9 +14472,6 @@
       <c r="O95" t="n">
         <v>9</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.01780800988653221</v>
       </c>
@@ -15269,9 +15209,6 @@
       <c r="O100" t="n">
         <v>11</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.0217653454168727</v>
       </c>
@@ -16009,9 +15946,6 @@
       <c r="O105" t="n">
         <v>12</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.02374401318204294</v>
       </c>
@@ -16897,9 +16831,6 @@
       <c r="O111" t="n">
         <v>2</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.003957335530340491</v>
       </c>
@@ -17635,9 +17566,6 @@
         <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
